--- a/Hitster_BE_208.xlsx
+++ b/Hitster_BE_208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/jakob_depeuter_student_kuleuven_be/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/jakob_depeuter_student_kuleuven_be/Documents/Documents/GitHub/hitster-be/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{CA620351-37C9-493E-AD22-44F3F236D7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{971C2B8D-2E4D-40BA-B9EA-C72DA295A5A5}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{CA620351-37C9-493E-AD22-44F3F236D7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD541156-B70B-4CF8-BEA7-F4F62B81545F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{7D5BECDE-3070-4858-9EF0-6742C2B48E55}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{7D5BECDE-3070-4858-9EF0-6742C2B48E55}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="629">
   <si>
     <t>Artiest</t>
   </si>
@@ -119,9 +119,6 @@
     <t>Buzzcocks</t>
   </si>
   <si>
-    <t>Ever Fallen in Love (With Someone You Shouldn't've?) - 1996 Remastered Version</t>
-  </si>
-  <si>
     <t>spotify:track:5YUJMvTg4AWHKjqQidTsGK</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
     <t>Iron Maiden</t>
   </si>
   <si>
-    <t>Wasted Years - 2015 Remaster</t>
-  </si>
-  <si>
     <t>spotify:track:1HM7Vp84E4SMzdrZONg6bH</t>
   </si>
   <si>
@@ -479,9 +473,6 @@
     <t>Led Zeppelin</t>
   </si>
   <si>
-    <t>Kashmir - Remaster</t>
-  </si>
-  <si>
     <t>spotify:track:6Vjk8MNXpQpi0F4BefdTyq</t>
   </si>
   <si>
@@ -542,27 +533,18 @@
     <t>Queen</t>
   </si>
   <si>
-    <t>Bicycle Race - Remastered 2011</t>
-  </si>
-  <si>
     <t>spotify:track:5CTAcf8aS0a0sIsDwQRF9C</t>
   </si>
   <si>
     <t>Michael Jackson</t>
   </si>
   <si>
-    <t>Rock with You - Single Version</t>
-  </si>
-  <si>
     <t>spotify:track:7oOOI85fVQvVnK5ynNMdW7</t>
   </si>
   <si>
     <t>Saxon</t>
   </si>
   <si>
-    <t>Wheels of Steel - 2009 Remaster</t>
-  </si>
-  <si>
     <t>spotify:track:181bQUGjSDPa0mZoPVGJes</t>
   </si>
   <si>
@@ -647,9 +629,6 @@
     <t>The Pointer Sisters</t>
   </si>
   <si>
-    <t>Jump (Original Mix)</t>
-  </si>
-  <si>
     <t>spotify:track:1kIu9zpYtWjgrLlsactlna</t>
   </si>
   <si>
@@ -692,9 +671,6 @@
     <t>Dire Straits</t>
   </si>
   <si>
-    <t>Brothers In Arms - Remastered 1996</t>
-  </si>
-  <si>
     <t>spotify:track:3elV4E1GOKfF0MVRgdp6eU</t>
   </si>
   <si>
@@ -854,9 +830,6 @@
     <t>Lionel Richie</t>
   </si>
   <si>
-    <t>All Night Long (All Night) - Single Version</t>
-  </si>
-  <si>
     <t>spotify:track:4czNORk5MjW5WOn98bki32</t>
   </si>
   <si>
@@ -1076,9 +1049,6 @@
     <t>spotify:track:75JFxkI2RXiU7L9VXzMkle</t>
   </si>
   <si>
-    <t>blink-182</t>
-  </si>
-  <si>
     <t>I Miss You</t>
   </si>
   <si>
@@ -1382,9 +1352,6 @@
     <t>Bobbejaan Schoepen</t>
   </si>
   <si>
-    <t>Ik zie zo gere m'n duivekot (Original</t>
-  </si>
-  <si>
     <t>Eddy Wally</t>
   </si>
   <si>
@@ -1640,9 +1607,6 @@
     <t>Metallica</t>
   </si>
   <si>
-    <t>Sad But True - Remastered 2021</t>
-  </si>
-  <si>
     <t>spotify:track:5ltXoDLlI0rFZAmOXbAp5T</t>
   </si>
   <si>
@@ -1718,9 +1682,6 @@
     <t>The Mamas &amp; The Papas</t>
   </si>
   <si>
-    <t>California Dreamin' - Single Version</t>
-  </si>
-  <si>
     <t>spotify:track:4s6LhHAV5SEsOV0lC2tjvJ</t>
   </si>
   <si>
@@ -1878,16 +1839,111 @@
   </si>
   <si>
     <t>spotify:track:3wvWM5Hy9QQVNQ6nf8t0k9</t>
+  </si>
+  <si>
+    <t>Ever Fallen in Love (With Someone You Shouldn't've?)</t>
+  </si>
+  <si>
+    <t>Kashmir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wheels of Steel </t>
+  </si>
+  <si>
+    <t>Wasted Years</t>
+  </si>
+  <si>
+    <t>Brothers In Arms</t>
+  </si>
+  <si>
+    <t>Bicycle Race</t>
+  </si>
+  <si>
+    <t>Sad But True</t>
+  </si>
+  <si>
+    <t>Ik zie zo gere m'n duivekot</t>
+  </si>
+  <si>
+    <t>All Night Long (All Night)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California Dreamin' </t>
+  </si>
+  <si>
+    <t>Rock with You</t>
+  </si>
+  <si>
+    <t>Blink-182</t>
+  </si>
+  <si>
+    <t>spotify:track:6TfBA04WJ3X1d1wXhaCFVT</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/6kwAbEjseqBob48jCus7Sz?si=2d5289b32eac4bbf</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/6RtPijgfPKROxEzTHNRiDp?si=63233cbae74b4052</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/0wYHz9rLGFjEyFrD7mpsr3?si=fc7b3b062d764b93</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/6K4t31amVTZDgR3sKmwUJJ?si=d2a74e4da24a4af1</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/2Z8WuEywRWYTKe1NybPQEW?si=9a9f717d5e7a43ac</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/3vv9phIu6Y1vX3jcqaGz5Z?si=2bcef36285d44d8c</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/2n1lYSf8iDfSIYEBZJsS99?si=3ea8b07135a14e29</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/23L5CiUhw2jV1OIMwthR3S?si=b9f4a986beb44f8e</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/5Ohxk2dO5COHF1krpoPigN?si=176526b924db4cb1</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/2x0RZdkZcD8QRI53XT4GI5?si=c16c0bfbcac34ba1</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/4V2eYSKckdvIbb3t20K3ga?si=eef5b0677d1a4204</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/2qSkIjg1o9h3YT9RAgYN75?si=1328b00af29b4079</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/5H1sKFMzDeMtXwND3V6hRY?si=357ef326359f4abb</t>
+  </si>
+  <si>
+    <t>End of Beginning</t>
+  </si>
+  <si>
+    <t>Djo</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/3qhlB30KknSejmIvZZLjOD?si=e50747bda4a8401b</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1910,16 +1966,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2252,11 +2311,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A5110F6-B0E1-49A9-913A-0C4666BCA3C5}">
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:D210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.21875" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2276,2880 +2336,2941 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>446</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>447</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>1950</v>
+        <v>2001</v>
       </c>
       <c r="D2" t="s">
-        <v>612</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>543</v>
+        <v>412</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>544</v>
+        <v>413</v>
       </c>
       <c r="C3">
-        <v>1954</v>
+        <v>1979</v>
       </c>
       <c r="D3" t="s">
-        <v>545</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>565</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>566</v>
       </c>
       <c r="C4">
-        <v>1956</v>
+        <v>2018</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>467</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>468</v>
       </c>
       <c r="C5">
-        <v>1957</v>
+        <v>2013</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>184</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="C6">
-        <v>1959</v>
+        <v>1982</v>
       </c>
       <c r="D6" t="s">
-        <v>236</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="C7">
-        <v>1959</v>
+        <v>1980</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>89</v>
+        <v>207</v>
       </c>
       <c r="C8">
-        <v>1960</v>
+        <v>1985</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>523</v>
+        <v>119</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>524</v>
+        <v>120</v>
       </c>
       <c r="C9">
-        <v>1960</v>
+        <v>1971</v>
       </c>
       <c r="D9" t="s">
-        <v>525</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>469</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>470</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>1962</v>
+        <v>1993</v>
       </c>
       <c r="D10" t="s">
-        <v>471</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>505</v>
+        <v>285</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>506</v>
+        <v>286</v>
       </c>
       <c r="C11">
-        <v>1962</v>
+        <v>1978</v>
       </c>
       <c r="D11" t="s">
-        <v>507</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>528</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>529</v>
       </c>
       <c r="C12">
-        <v>1963</v>
+        <v>1983</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>381</v>
+        <v>220</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>382</v>
+        <v>221</v>
       </c>
       <c r="C13">
-        <v>1963</v>
+        <v>1987</v>
       </c>
       <c r="D13" t="s">
-        <v>383</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>493</v>
+        <v>197</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>494</v>
+        <v>198</v>
       </c>
       <c r="C14">
-        <v>1963</v>
+        <v>1983</v>
       </c>
       <c r="D14" t="s">
-        <v>495</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>535</v>
+        <v>309</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>581</v>
+        <v>310</v>
       </c>
       <c r="C15">
-        <v>1963</v>
+        <v>2000</v>
       </c>
       <c r="D15" t="s">
-        <v>536</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>555</v>
+        <v>371</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>556</v>
+        <v>372</v>
       </c>
       <c r="C16">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="D16" t="s">
-        <v>557</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>231</v>
+        <v>318</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="C17">
-        <v>1965</v>
+        <v>2002</v>
       </c>
       <c r="D17" t="s">
-        <v>233</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>558</v>
+        <v>273</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>559</v>
+        <v>274</v>
       </c>
       <c r="C18">
-        <v>1965</v>
+        <v>1993</v>
       </c>
       <c r="D18" t="s">
-        <v>560</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="C19">
-        <v>1966</v>
+        <v>1976</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>223</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="C20">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>372</v>
+        <v>122</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>373</v>
+        <v>123</v>
       </c>
       <c r="C21">
-        <v>1966</v>
+        <v>1971</v>
       </c>
       <c r="D21" t="s">
-        <v>374</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="C22">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="D22" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>353</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>98</v>
+        <v>354</v>
       </c>
       <c r="C23">
-        <v>1968</v>
+        <v>2005</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="C24">
-        <v>1968</v>
+        <v>1977</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>433</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>104</v>
+        <v>434</v>
       </c>
       <c r="C25">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
+        <v>435</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>400</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="C26">
-        <v>1969</v>
+        <v>2008</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>109</v>
+        <v>386</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>110</v>
+        <v>387</v>
       </c>
       <c r="C27">
-        <v>1969</v>
+        <v>2007</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>389</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>113</v>
+        <v>390</v>
       </c>
       <c r="C28">
-        <v>1969</v>
+        <v>2007</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>391</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>443</v>
+        <v>362</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>444</v>
+        <v>363</v>
       </c>
       <c r="C29">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="D29" t="s">
-        <v>445</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="C30">
-        <v>1970</v>
+        <v>2001</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>267</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>119</v>
+        <v>268</v>
       </c>
       <c r="C31">
-        <v>1970</v>
+        <v>1993</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>502</v>
+        <v>270</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>503</v>
+        <v>271</v>
       </c>
       <c r="C32">
-        <v>1970</v>
+        <v>1993</v>
       </c>
       <c r="D32" t="s">
-        <v>504</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>508</v>
+        <v>95</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>509</v>
+        <v>96</v>
       </c>
       <c r="C33">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="D33" t="s">
-        <v>510</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>566</v>
+        <v>167</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="C34">
-        <v>1970</v>
+        <v>1980</v>
       </c>
       <c r="D34" t="s">
-        <v>567</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>347</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>122</v>
+        <v>348</v>
       </c>
       <c r="C35">
-        <v>1971</v>
+        <v>2004</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C36">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C37">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="D37" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C38">
-        <v>1972</v>
+        <v>1977</v>
       </c>
       <c r="D38" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>525</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>131</v>
+        <v>526</v>
       </c>
       <c r="C39">
-        <v>1972</v>
+        <v>2022</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>527</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>297</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>137</v>
+        <v>298</v>
       </c>
       <c r="C40">
-        <v>1972</v>
+        <v>1998</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>454</v>
+        <v>276</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>455</v>
+        <v>277</v>
       </c>
       <c r="C41">
-        <v>1972</v>
+        <v>1994</v>
       </c>
       <c r="D41" t="s">
-        <v>456</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>415</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>11</v>
+        <v>416</v>
       </c>
       <c r="C42">
-        <v>1973</v>
+        <v>1980</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>417</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>344</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="C43">
-        <v>1973</v>
+        <v>2000</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>346</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>490</v>
+        <v>324</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>491</v>
+        <v>325</v>
       </c>
       <c r="C44">
-        <v>1973</v>
+        <v>2002</v>
       </c>
       <c r="D44" t="s">
-        <v>492</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>139</v>
+        <v>330</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>140</v>
+        <v>331</v>
       </c>
       <c r="C45">
-        <v>1974</v>
+        <v>2002</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>332</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="C46">
-        <v>1974</v>
+        <v>1987</v>
       </c>
       <c r="D46" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>249</v>
+        <v>48</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>250</v>
+        <v>603</v>
       </c>
       <c r="C47">
-        <v>1974</v>
+        <v>1986</v>
       </c>
       <c r="D47" t="s">
-        <v>251</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="C48">
-        <v>1975</v>
+        <v>1988</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>149</v>
+        <v>573</v>
       </c>
       <c r="C49">
-        <v>1975</v>
+        <v>1983</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>151</v>
+        <v>551</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>152</v>
+        <v>594</v>
       </c>
       <c r="C50">
-        <v>1975</v>
+        <v>2008</v>
       </c>
       <c r="D50" t="s">
-        <v>153</v>
+        <v>552</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>514</v>
+        <v>42</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>515</v>
+        <v>43</v>
       </c>
       <c r="C51">
-        <v>1975</v>
+        <v>1982</v>
       </c>
       <c r="D51" t="s">
-        <v>516</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>611</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="C52">
-        <v>1976</v>
+        <v>2003</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>337</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>229</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>17</v>
+        <v>230</v>
       </c>
       <c r="C53">
-        <v>1976</v>
+        <v>1987</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>154</v>
+        <v>543</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>155</v>
+        <v>544</v>
       </c>
       <c r="C54">
-        <v>1976</v>
+        <v>1964</v>
       </c>
       <c r="D54" t="s">
-        <v>156</v>
+        <v>545</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C55">
-        <v>1976</v>
+        <v>1970</v>
       </c>
       <c r="D55" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>348</v>
+        <v>92</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>349</v>
+        <v>93</v>
       </c>
       <c r="C56">
-        <v>1976</v>
+        <v>1966</v>
       </c>
       <c r="D56" t="s">
-        <v>350</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>548</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>20</v>
+        <v>549</v>
       </c>
       <c r="C57">
-        <v>1977</v>
+        <v>2001</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>550</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>23</v>
+        <v>483</v>
       </c>
       <c r="C58">
-        <v>1977</v>
+        <v>1963</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>484</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="C59">
-        <v>1977</v>
+        <v>1956</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>163</v>
+        <v>300</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>164</v>
+        <v>301</v>
       </c>
       <c r="C60">
-        <v>1977</v>
+        <v>1998</v>
       </c>
       <c r="D60" t="s">
-        <v>165</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="C61">
-        <v>1977</v>
+        <v>1996</v>
       </c>
       <c r="D61" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>350</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
       <c r="C62">
-        <v>1978</v>
+        <v>2005</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>166</v>
+        <v>509</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>167</v>
+        <v>510</v>
       </c>
       <c r="C63">
-        <v>1978</v>
+        <v>2020</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>511</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="C64">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="D64" t="s">
-        <v>296</v>
+        <v>243</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="C65">
-        <v>1979</v>
+        <v>1983</v>
       </c>
       <c r="D65" t="s">
-        <v>33</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>291</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>35</v>
+        <v>292</v>
       </c>
       <c r="C66">
-        <v>1979</v>
+        <v>1997</v>
       </c>
       <c r="D66" t="s">
-        <v>36</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="C67">
-        <v>1979</v>
+        <v>1968</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="C68">
-        <v>1979</v>
+        <v>1986</v>
       </c>
       <c r="D68" t="s">
-        <v>254</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>422</v>
+        <v>531</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>423</v>
+        <v>532</v>
       </c>
       <c r="C69">
-        <v>1979</v>
+        <v>1954</v>
       </c>
       <c r="D69" t="s">
-        <v>424</v>
+        <v>533</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>428</v>
+        <v>380</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>429</v>
+        <v>381</v>
       </c>
       <c r="C70">
-        <v>1979</v>
+        <v>2006</v>
       </c>
       <c r="D70" t="s">
-        <v>430</v>
+        <v>382</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C71">
-        <v>1980</v>
+        <v>1969</v>
       </c>
       <c r="D71" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>172</v>
+        <v>479</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>173</v>
+        <v>480</v>
       </c>
       <c r="C72">
-        <v>1980</v>
+        <v>1973</v>
       </c>
       <c r="D72" t="s">
-        <v>174</v>
+        <v>481</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>175</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>176</v>
+        <v>190</v>
+      </c>
+      <c r="B73" s="1">
+        <v>1999</v>
       </c>
       <c r="C73">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="D73" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C74">
-        <v>1980</v>
+        <v>1984</v>
       </c>
       <c r="D74" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>426</v>
+        <v>78</v>
       </c>
       <c r="C75">
-        <v>1980</v>
+        <v>2000</v>
       </c>
       <c r="D75" t="s">
-        <v>427</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="C76">
-        <v>1981</v>
+        <v>1959</v>
       </c>
       <c r="D76" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>178</v>
+        <v>534</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>179</v>
+        <v>535</v>
       </c>
       <c r="C77">
-        <v>1981</v>
+        <v>2025</v>
       </c>
       <c r="D77" t="s">
-        <v>180</v>
+        <v>536</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="C78">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="D78" t="s">
-        <v>183</v>
+        <v>240</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>184</v>
+        <v>392</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>185</v>
+        <v>393</v>
       </c>
       <c r="C79">
-        <v>1981</v>
+        <v>2007</v>
       </c>
       <c r="D79" t="s">
-        <v>186</v>
+        <v>394</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>405</v>
+        <v>256</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>406</v>
+        <v>257</v>
       </c>
       <c r="C80">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="D80" t="s">
-        <v>407</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>43</v>
+        <v>341</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>44</v>
+        <v>342</v>
       </c>
       <c r="C81">
-        <v>1982</v>
+        <v>2003</v>
       </c>
       <c r="D81" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>190</v>
+        <v>418</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>191</v>
+        <v>419</v>
       </c>
       <c r="C82">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="D82" t="s">
-        <v>192</v>
+        <v>420</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>193</v>
+        <v>497</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>194</v>
+        <v>498</v>
       </c>
       <c r="C83">
-        <v>1982</v>
+        <v>1970</v>
       </c>
       <c r="D83" t="s">
-        <v>195</v>
+        <v>499</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>196</v>
-      </c>
-      <c r="B84" s="1">
-        <v>1999</v>
+        <v>62</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C84">
-        <v>1982</v>
+        <v>1996</v>
       </c>
       <c r="D84" t="s">
-        <v>197</v>
+        <v>64</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>472</v>
+        <v>148</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>473</v>
+        <v>149</v>
       </c>
       <c r="C85">
-        <v>1982</v>
+        <v>1975</v>
       </c>
       <c r="D85" t="s">
-        <v>474</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>199</v>
+        <v>117</v>
       </c>
       <c r="C86">
-        <v>1983</v>
+        <v>1970</v>
       </c>
       <c r="D86" t="s">
-        <v>200</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>201</v>
+        <v>368</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>202</v>
+        <v>369</v>
       </c>
       <c r="C87">
-        <v>1983</v>
+        <v>2006</v>
       </c>
       <c r="D87" t="s">
-        <v>203</v>
+        <v>370</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>205</v>
+        <v>604</v>
       </c>
       <c r="C88">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="D88" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>207</v>
+        <v>452</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>208</v>
+        <v>453</v>
       </c>
       <c r="C89">
-        <v>1983</v>
+        <v>2009</v>
       </c>
       <c r="D89" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>270</v>
+        <v>68</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>271</v>
+        <v>69</v>
       </c>
       <c r="C90">
-        <v>1983</v>
+        <v>2001</v>
       </c>
       <c r="D90" t="s">
-        <v>272</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>540</v>
+        <v>247</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>541</v>
+        <v>248</v>
       </c>
       <c r="C91">
-        <v>1983</v>
+        <v>1990</v>
       </c>
       <c r="D91" t="s">
-        <v>542</v>
+        <v>249</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="C92">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="D92" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>261</v>
+        <v>437</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>262</v>
+        <v>438</v>
       </c>
       <c r="C93">
-        <v>1984</v>
+        <v>1966</v>
       </c>
       <c r="D93" t="s">
-        <v>263</v>
+        <v>439</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>529</v>
+        <v>226</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>530</v>
+        <v>227</v>
       </c>
       <c r="C94">
-        <v>1984</v>
+        <v>1959</v>
       </c>
       <c r="D94" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>213</v>
+        <v>377</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>214</v>
+        <v>378</v>
       </c>
       <c r="C95">
-        <v>1985</v>
+        <v>1989</v>
       </c>
       <c r="D95" t="s">
-        <v>215</v>
+        <v>379</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>216</v>
+        <v>374</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>217</v>
+        <v>375</v>
       </c>
       <c r="C96">
-        <v>1985</v>
+        <v>2006</v>
       </c>
       <c r="D96" t="s">
-        <v>218</v>
+        <v>376</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>46</v>
+        <v>440</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>47</v>
+        <v>441</v>
       </c>
       <c r="C97">
-        <v>1986</v>
+        <v>2011</v>
       </c>
       <c r="D97" t="s">
-        <v>48</v>
+        <v>442</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>49</v>
+        <v>557</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>50</v>
+        <v>595</v>
       </c>
       <c r="C98">
-        <v>1986</v>
+        <v>2011</v>
       </c>
       <c r="D98" t="s">
-        <v>51</v>
+        <v>558</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="C99">
-        <v>1986</v>
+        <v>1972</v>
       </c>
       <c r="D99" t="s">
-        <v>221</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>222</v>
+        <v>125</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>223</v>
+        <v>126</v>
       </c>
       <c r="C100">
-        <v>1986</v>
+        <v>1971</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>127</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>517</v>
+        <v>436</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>518</v>
+        <v>607</v>
       </c>
       <c r="C101">
-        <v>1986</v>
+        <v>1950</v>
       </c>
       <c r="D101" t="s">
-        <v>519</v>
+        <v>599</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="C102">
-        <v>1987</v>
+        <v>1968</v>
       </c>
       <c r="D102" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>228</v>
+        <v>395</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>229</v>
+        <v>396</v>
       </c>
       <c r="C103">
-        <v>1987</v>
+        <v>1981</v>
       </c>
       <c r="D103" t="s">
-        <v>230</v>
+        <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>238</v>
+        <v>179</v>
       </c>
       <c r="C104">
-        <v>1987</v>
+        <v>1981</v>
       </c>
       <c r="D104" t="s">
-        <v>239</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>55</v>
+        <v>523</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>56</v>
+        <v>568</v>
       </c>
       <c r="C105">
-        <v>1988</v>
+        <v>1963</v>
       </c>
       <c r="D105" t="s">
-        <v>57</v>
+        <v>524</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>243</v>
+        <v>160</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>244</v>
+        <v>161</v>
       </c>
       <c r="C106">
-        <v>1988</v>
+        <v>1977</v>
       </c>
       <c r="D106" t="s">
-        <v>245</v>
+        <v>162</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="C107">
-        <v>1989</v>
+        <v>1981</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C108">
         <v>1989</v>
       </c>
       <c r="D108" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>246</v>
+        <v>464</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>247</v>
+        <v>465</v>
       </c>
       <c r="C109">
-        <v>1989</v>
+        <v>2013</v>
       </c>
       <c r="D109" t="s">
-        <v>248</v>
+        <v>466</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>330</v>
+        <v>403</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>331</v>
+        <v>404</v>
       </c>
       <c r="C110">
-        <v>1989</v>
+        <v>2009</v>
       </c>
       <c r="D110" t="s">
-        <v>332</v>
+        <v>405</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>387</v>
+        <v>515</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>388</v>
+        <v>516</v>
       </c>
       <c r="C111">
-        <v>1989</v>
+        <v>2021</v>
       </c>
       <c r="D111" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>255</v>
+        <v>86</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>87</v>
       </c>
       <c r="C112">
-        <v>1990</v>
+        <v>1960</v>
       </c>
       <c r="D112" t="s">
-        <v>257</v>
+        <v>88</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>259</v>
+        <v>313</v>
       </c>
       <c r="C113">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="D113" t="s">
-        <v>260</v>
+        <v>314</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C114">
-        <v>1990</v>
+        <v>1984</v>
       </c>
       <c r="D114" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>267</v>
+        <v>518</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>268</v>
+        <v>519</v>
       </c>
       <c r="C115">
-        <v>1991</v>
+        <v>1984</v>
       </c>
       <c r="D115" t="s">
-        <v>269</v>
+        <v>520</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>532</v>
+        <v>409</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>533</v>
+        <v>410</v>
       </c>
       <c r="C116">
-        <v>1991</v>
+        <v>2009</v>
       </c>
       <c r="D116" t="s">
-        <v>534</v>
+        <v>411</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>274</v>
+        <v>608</v>
       </c>
       <c r="C117">
-        <v>1992</v>
+        <v>1983</v>
       </c>
       <c r="D117" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>365</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>62</v>
+        <v>366</v>
       </c>
       <c r="C118">
-        <v>1993</v>
+        <v>2006</v>
       </c>
       <c r="D118" t="s">
-        <v>63</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>276</v>
+        <v>476</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>277</v>
+        <v>477</v>
       </c>
       <c r="C119">
-        <v>1993</v>
+        <v>2014</v>
       </c>
       <c r="D119" t="s">
-        <v>278</v>
+        <v>478</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>279</v>
+        <v>470</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>280</v>
+        <v>471</v>
       </c>
       <c r="C120">
-        <v>1993</v>
+        <v>2014</v>
       </c>
       <c r="D120" t="s">
-        <v>281</v>
+        <v>472</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>282</v>
+        <v>151</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>283</v>
+        <v>152</v>
       </c>
       <c r="C121">
-        <v>1993</v>
+        <v>1976</v>
       </c>
       <c r="D121" t="s">
-        <v>284</v>
+        <v>153</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>285</v>
+        <v>145</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>286</v>
+        <v>146</v>
       </c>
       <c r="C122">
-        <v>1994</v>
+        <v>1975</v>
       </c>
       <c r="D122" t="s">
-        <v>287</v>
+        <v>147</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="C123">
-        <v>1994</v>
+        <v>1997</v>
       </c>
       <c r="D123" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>64</v>
+        <v>488</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>65</v>
+        <v>489</v>
       </c>
       <c r="C124">
-        <v>1996</v>
+        <v>2016</v>
       </c>
       <c r="D124" t="s">
-        <v>66</v>
+        <v>490</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>288</v>
+        <v>10</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>289</v>
+        <v>11</v>
       </c>
       <c r="C125">
-        <v>1996</v>
+        <v>1973</v>
       </c>
       <c r="D125" t="s">
-        <v>290</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>291</v>
+        <v>36</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>292</v>
+        <v>37</v>
       </c>
       <c r="C126">
-        <v>1996</v>
+        <v>1980</v>
       </c>
       <c r="D126" t="s">
-        <v>293</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>297</v>
+        <v>217</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>298</v>
+        <v>218</v>
       </c>
       <c r="C127">
-        <v>1996</v>
+        <v>1977</v>
       </c>
       <c r="D127" t="s">
-        <v>299</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>300</v>
+        <v>546</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>301</v>
+        <v>609</v>
       </c>
       <c r="C128">
-        <v>1997</v>
+        <v>1965</v>
       </c>
       <c r="D128" t="s">
-        <v>302</v>
+        <v>547</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="C129">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="D129" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>306</v>
+        <v>19</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="C130">
-        <v>1998</v>
+        <v>1977</v>
       </c>
       <c r="D130" t="s">
-        <v>308</v>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>309</v>
+        <v>506</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>310</v>
+        <v>507</v>
       </c>
       <c r="C131">
-        <v>1998</v>
+        <v>1986</v>
       </c>
       <c r="D131" t="s">
-        <v>311</v>
+        <v>508</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>312</v>
+        <v>424</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>313</v>
+        <v>425</v>
       </c>
       <c r="C132">
-        <v>1998</v>
+        <v>2010</v>
       </c>
       <c r="D132" t="s">
-        <v>314</v>
+        <v>426</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>315</v>
+        <v>200</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>316</v>
+        <v>201</v>
       </c>
       <c r="C133">
-        <v>1999</v>
+        <v>1983</v>
       </c>
       <c r="D133" t="s">
-        <v>317</v>
+        <v>202</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>67</v>
+        <v>315</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>68</v>
+        <v>316</v>
       </c>
       <c r="C134">
-        <v>2000</v>
+        <v>1994</v>
       </c>
       <c r="D134" t="s">
-        <v>69</v>
+        <v>317</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>79</v>
+        <v>559</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="C135">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="D135" t="s">
-        <v>81</v>
+        <v>561</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>318</v>
+        <v>33</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>319</v>
+        <v>34</v>
       </c>
       <c r="C136">
-        <v>2000</v>
+        <v>1979</v>
       </c>
       <c r="D136" t="s">
-        <v>320</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>321</v>
+        <v>140</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>322</v>
+        <v>141</v>
       </c>
       <c r="C137">
-        <v>2000</v>
+        <v>1974</v>
       </c>
       <c r="D137" t="s">
-        <v>323</v>
+        <v>142</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>354</v>
+        <v>406</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="C138">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="D138" t="s">
-        <v>356</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C139">
-        <v>2001</v>
+        <v>1986</v>
       </c>
       <c r="D139" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>73</v>
+        <v>430</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>74</v>
+        <v>431</v>
       </c>
       <c r="C140">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="D140" t="s">
-        <v>75</v>
+        <v>432</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>77</v>
+        <v>605</v>
       </c>
       <c r="C141">
-        <v>2001</v>
+        <v>1978</v>
       </c>
       <c r="D141" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>336</v>
+        <v>65</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>337</v>
+        <v>66</v>
       </c>
       <c r="C142">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D142" t="s">
-        <v>338</v>
+        <v>67</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>561</v>
+        <v>181</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>562</v>
+        <v>182</v>
       </c>
       <c r="C143">
-        <v>2001</v>
+        <v>1980</v>
       </c>
       <c r="D143" t="s">
-        <v>563</v>
+        <v>183</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="C144">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="D144" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C145">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="D145" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>339</v>
+        <v>427</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>340</v>
+        <v>428</v>
       </c>
       <c r="C146">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="D146" t="s">
-        <v>341</v>
+        <v>429</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>342</v>
+        <v>279</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>343</v>
+        <v>280</v>
       </c>
       <c r="C147">
-        <v>2002</v>
+        <v>1996</v>
       </c>
       <c r="D147" t="s">
-        <v>344</v>
+        <v>281</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>573</v>
+        <v>606</v>
       </c>
       <c r="C148">
-        <v>2002</v>
+        <v>1991</v>
       </c>
       <c r="D148" t="s">
-        <v>574</v>
+        <v>522</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>345</v>
+        <v>288</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>346</v>
+        <v>289</v>
       </c>
       <c r="C149">
-        <v>2003</v>
+        <v>1996</v>
       </c>
       <c r="D149" t="s">
-        <v>347</v>
+        <v>290</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>351</v>
+        <v>4</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>352</v>
+        <v>5</v>
       </c>
       <c r="C150">
-        <v>2003</v>
+        <v>1957</v>
       </c>
       <c r="D150" t="s">
-        <v>353</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>357</v>
+        <v>250</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>358</v>
+        <v>251</v>
       </c>
       <c r="C151">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="D151" t="s">
-        <v>359</v>
+        <v>252</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>360</v>
+        <v>16</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>361</v>
+        <v>17</v>
       </c>
       <c r="C152">
-        <v>2005</v>
+        <v>1976</v>
       </c>
       <c r="D152" t="s">
-        <v>362</v>
+        <v>18</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>363</v>
+        <v>264</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>364</v>
+        <v>265</v>
       </c>
       <c r="C153">
-        <v>2005</v>
+        <v>1992</v>
       </c>
       <c r="D153" t="s">
-        <v>365</v>
+        <v>266</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>366</v>
+        <v>503</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>367</v>
+        <v>504</v>
       </c>
       <c r="C154">
-        <v>2005</v>
+        <v>1975</v>
       </c>
       <c r="D154" t="s">
-        <v>368</v>
+        <v>505</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>369</v>
+        <v>321</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>370</v>
+        <v>322</v>
       </c>
       <c r="C155">
-        <v>2005</v>
+        <v>1989</v>
       </c>
       <c r="D155" t="s">
-        <v>371</v>
+        <v>323</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>375</v>
+        <v>172</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>376</v>
+        <v>173</v>
       </c>
       <c r="C156">
-        <v>2006</v>
+        <v>1981</v>
       </c>
       <c r="D156" t="s">
-        <v>377</v>
+        <v>174</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>378</v>
+        <v>13</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>379</v>
+        <v>14</v>
       </c>
       <c r="C157">
-        <v>2006</v>
+        <v>1976</v>
       </c>
       <c r="D157" t="s">
-        <v>380</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>384</v>
+        <v>27</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>385</v>
+        <v>28</v>
       </c>
       <c r="C158">
-        <v>2006</v>
+        <v>1963</v>
       </c>
       <c r="D158" t="s">
-        <v>386</v>
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>390</v>
+        <v>537</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>391</v>
+        <v>538</v>
       </c>
       <c r="C159">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="D159" t="s">
-        <v>392</v>
+        <v>539</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>393</v>
+        <v>259</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>394</v>
+        <v>260</v>
       </c>
       <c r="C160">
-        <v>2007</v>
+        <v>1991</v>
       </c>
       <c r="D160" t="s">
-        <v>395</v>
+        <v>261</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>396</v>
+        <v>338</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>397</v>
+        <v>339</v>
       </c>
       <c r="C161">
-        <v>2007</v>
+        <v>1976</v>
       </c>
       <c r="D161" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>399</v>
+        <v>25</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C162">
-        <v>2007</v>
+        <v>1978</v>
       </c>
       <c r="D162" t="s">
-        <v>401</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>402</v>
+        <v>39</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>403</v>
+        <v>40</v>
       </c>
       <c r="C163">
-        <v>2007</v>
+        <v>1981</v>
       </c>
       <c r="D163" t="s">
-        <v>404</v>
+        <v>41</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>410</v>
+        <v>244</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>411</v>
+        <v>245</v>
       </c>
       <c r="C164">
-        <v>2008</v>
+        <v>1979</v>
       </c>
       <c r="D164" t="s">
-        <v>412</v>
+        <v>246</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>416</v>
+        <v>7</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>417</v>
+        <v>8</v>
       </c>
       <c r="C165">
-        <v>2008</v>
+        <v>1972</v>
       </c>
       <c r="D165" t="s">
-        <v>418</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>564</v>
+        <v>449</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>607</v>
+        <v>450</v>
       </c>
       <c r="C166">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="D166" t="s">
-        <v>565</v>
+        <v>451</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>408</v>
+        <v>540</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>409</v>
+        <v>541</v>
       </c>
       <c r="C167">
-        <v>2008</v>
+        <v>2023</v>
+      </c>
+      <c r="D167" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>413</v>
+        <v>555</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>414</v>
+        <v>596</v>
       </c>
       <c r="C168">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D168" t="s">
-        <v>415</v>
+        <v>556</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>419</v>
+        <v>461</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="C169">
-        <v>2009</v>
+        <v>1982</v>
       </c>
       <c r="D169" t="s">
-        <v>421</v>
+        <v>463</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>441</v>
+        <v>501</v>
       </c>
       <c r="C170">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="D170" t="s">
-        <v>442</v>
+        <v>502</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="C171">
-        <v>2009</v>
+        <v>1972</v>
       </c>
       <c r="D171" t="s">
-        <v>465</v>
+        <v>445</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>575</v>
+        <v>383</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>576</v>
+        <v>384</v>
       </c>
       <c r="C172">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="D172" t="s">
-        <v>577</v>
+        <v>385</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>431</v>
+        <v>110</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>432</v>
+        <v>111</v>
       </c>
       <c r="C173">
-        <v>2010</v>
+        <v>1969</v>
       </c>
       <c r="D173" t="s">
-        <v>433</v>
+        <v>112</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>434</v>
+        <v>306</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>435</v>
+        <v>307</v>
       </c>
       <c r="C174">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>308</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>437</v>
+        <v>491</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>438</v>
+        <v>492</v>
       </c>
       <c r="C175">
-        <v>2010</v>
+        <v>1970</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>493</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>451</v>
+        <v>494</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>452</v>
+        <v>495</v>
       </c>
       <c r="C176">
-        <v>2011</v>
+        <v>1962</v>
       </c>
       <c r="D176" t="s">
-        <v>453</v>
+        <v>496</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>568</v>
+        <v>104</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>609</v>
+        <v>105</v>
       </c>
       <c r="C177">
-        <v>2011</v>
+        <v>1969</v>
       </c>
       <c r="D177" t="s">
-        <v>569</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>570</v>
+        <v>56</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>608</v>
+        <v>57</v>
       </c>
       <c r="C178">
-        <v>2011</v>
+        <v>1989</v>
       </c>
       <c r="D178" t="s">
-        <v>571</v>
+        <v>58</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="C179">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D179" t="s">
-        <v>459</v>
+        <v>423</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>460</v>
+        <v>143</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>461</v>
+        <v>601</v>
       </c>
       <c r="C180">
-        <v>2012</v>
+        <v>1975</v>
       </c>
       <c r="D180" t="s">
-        <v>462</v>
+        <v>144</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>466</v>
+        <v>303</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>467</v>
+        <v>304</v>
       </c>
       <c r="C181">
-        <v>2012</v>
+        <v>1998</v>
       </c>
       <c r="D181" t="s">
-        <v>468</v>
+        <v>305</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="C182">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="D182" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>478</v>
+        <v>89</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>479</v>
+        <v>90</v>
       </c>
       <c r="C183">
-        <v>2013</v>
+        <v>1966</v>
       </c>
       <c r="D183" t="s">
-        <v>480</v>
+        <v>91</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>484</v>
+        <v>333</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>485</v>
+        <v>334</v>
       </c>
       <c r="C184">
-        <v>2013</v>
+        <v>2002</v>
       </c>
       <c r="D184" t="s">
-        <v>486</v>
+        <v>335</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>589</v>
+        <v>30</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>590</v>
+        <v>31</v>
       </c>
       <c r="C185">
-        <v>2013</v>
+        <v>1979</v>
+      </c>
+      <c r="D185" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>481</v>
+        <v>214</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>482</v>
+        <v>215</v>
       </c>
       <c r="C186">
-        <v>2014</v>
+        <v>1986</v>
       </c>
       <c r="D186" t="s">
-        <v>483</v>
+        <v>216</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="C187">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D187" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>593</v>
+        <v>455</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>594</v>
+        <v>456</v>
       </c>
       <c r="C188">
-        <v>2014</v>
+        <v>2012</v>
+      </c>
+      <c r="D188" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>595</v>
+        <v>512</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>596</v>
+        <v>513</v>
       </c>
       <c r="C189">
-        <v>2014</v>
+        <v>1960</v>
+      </c>
+      <c r="D189" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>496</v>
+        <v>53</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>497</v>
+        <v>54</v>
       </c>
       <c r="C190">
-        <v>2015</v>
+        <v>1988</v>
       </c>
       <c r="D190" t="s">
-        <v>498</v>
+        <v>55</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>597</v>
+        <v>553</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>598</v>
+        <v>569</v>
       </c>
       <c r="C191">
-        <v>2015</v>
+        <v>1970</v>
+      </c>
+      <c r="D191" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>599</v>
+        <v>446</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
       <c r="C192">
-        <v>2015</v>
+        <v>2012</v>
+      </c>
+      <c r="D192" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>601</v>
+        <v>137</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>602</v>
+        <v>138</v>
       </c>
       <c r="C193">
-        <v>2015</v>
+        <v>1974</v>
+      </c>
+      <c r="D193" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>499</v>
+        <v>562</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>500</v>
+        <v>563</v>
       </c>
       <c r="C194">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="D194" t="s">
-        <v>501</v>
+        <v>564</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>603</v>
+        <v>165</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="C195">
-        <v>2016</v>
+        <v>1979</v>
+      </c>
+      <c r="D195" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>605</v>
+        <v>398</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>606</v>
+        <v>399</v>
       </c>
       <c r="C196">
-        <v>2016</v>
+        <v>2008</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>511</v>
+        <v>576</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>512</v>
+        <v>577</v>
       </c>
       <c r="C197">
-        <v>2017</v>
-      </c>
-      <c r="D197" t="s">
-        <v>513</v>
+        <v>2013</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="C198">
-        <v>2017</v>
+        <v>2014</v>
+      </c>
+      <c r="D198" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C199">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="D199" t="s">
-        <v>580</v>
+        <v>615</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="C200">
-        <v>2019</v>
+        <v>2015</v>
+      </c>
+      <c r="D200" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>520</v>
+        <v>586</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>521</v>
+        <v>587</v>
       </c>
       <c r="C201">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D201" t="s">
-        <v>522</v>
+        <v>617</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>526</v>
+        <v>588</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>527</v>
+        <v>589</v>
       </c>
       <c r="C202">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="D202" t="s">
-        <v>528</v>
+        <v>618</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>537</v>
+        <v>590</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>538</v>
+        <v>591</v>
       </c>
       <c r="C203">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="D203" t="s">
-        <v>539</v>
+        <v>619</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C204">
-        <v>2022</v>
+        <v>2016</v>
+      </c>
+      <c r="D204" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>553</v>
+        <v>579</v>
       </c>
       <c r="C205">
-        <v>2023</v>
-      </c>
-      <c r="D205" t="s">
-        <v>554</v>
+        <v>2017</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>549</v>
+        <v>598</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>550</v>
+        <v>597</v>
       </c>
       <c r="C206">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="D206" t="s">
-        <v>551</v>
+        <v>622</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="C207">
-        <v>2024</v>
+        <v>2022</v>
+      </c>
+      <c r="D207" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="C208">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D208" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="C209">
         <v>2025</v>
+      </c>
+      <c r="D209" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>627</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C210">
+        <v>2022</v>
+      </c>
+      <c r="D210" t="s">
+        <v>628</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{7A5110F6-B0E1-49A9-913A-0C4666BCA3C5}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D209">
-      <sortCondition ref="C1"/>
+      <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="D196" r:id="rId1" display="https://open.spotify.com/track/6TfBA04WJ3X1d1wXhaCFVT?si=256b761b9b36429b" xr:uid="{0496E95B-E7C8-42CF-AD44-FA16D389EFDF}"/>
+    <hyperlink ref="D197" r:id="rId2" xr:uid="{B506D318-9113-4D07-A4C6-B50CDACD7993}"/>
+    <hyperlink ref="D205" r:id="rId3" xr:uid="{126F7FBE-D80C-4D98-A183-26D320DEFF60}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>